--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9851351746963</v>
+        <v>9.260084465888148</v>
       </c>
       <c r="D2" t="n">
-        <v>35.69495296017338</v>
+        <v>5.800429856028175</v>
       </c>
       <c r="E2" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F2" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.92208373373185</v>
+        <v>5.837338606731426</v>
       </c>
       <c r="D3" t="n">
-        <v>6.671872967082699</v>
+        <v>1.084179357150939</v>
       </c>
       <c r="E3" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F3" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.97947104600279</v>
+        <v>2.271664044975453</v>
       </c>
       <c r="D4" t="n">
-        <v>15.02607022645192</v>
+        <v>2.441736411798437</v>
       </c>
       <c r="E4" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F4" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.65319394117397</v>
+        <v>4.00614401544077</v>
       </c>
       <c r="D5" t="n">
-        <v>22.98321682913166</v>
+        <v>3.734772734733895</v>
       </c>
       <c r="E5" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F5" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.90923040152697</v>
+        <v>2.097749940248132</v>
       </c>
       <c r="D6" t="n">
-        <v>16.13416526432578</v>
+        <v>2.621801855452939</v>
       </c>
       <c r="E6" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F6" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.52112071323259</v>
+        <v>4.634682115900296</v>
       </c>
       <c r="D7" t="n">
-        <v>25.84724808396181</v>
+        <v>4.200177813643793</v>
       </c>
       <c r="E7" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F7" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.19380833580398</v>
+        <v>2.793993854568146</v>
       </c>
       <c r="D8" t="n">
-        <v>19.14220844029411</v>
+        <v>3.110608871547792</v>
       </c>
       <c r="E8" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F8" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.96559294626199</v>
+        <v>5.681908853767574</v>
       </c>
       <c r="D9" t="n">
-        <v>31.89752714243459</v>
+        <v>5.183348160645621</v>
       </c>
       <c r="E9" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F9" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.21673930120954</v>
+        <v>4.747720136446551</v>
       </c>
       <c r="D10" t="n">
-        <v>27.51168191368221</v>
+        <v>4.47064831097336</v>
       </c>
       <c r="E10" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F10" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.73573752023166</v>
+        <v>4.344557347037644</v>
       </c>
       <c r="D11" t="n">
-        <v>25.09723261160361</v>
+        <v>4.078300299385587</v>
       </c>
       <c r="E11" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F11" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.16691870214457</v>
+        <v>6.527124289098493</v>
       </c>
       <c r="D12" t="n">
-        <v>39.61454169342675</v>
+        <v>6.437363025181847</v>
       </c>
       <c r="E12" t="n">
-        <v>12.20702034191801</v>
+        <v>1.983640805561676</v>
       </c>
       <c r="F12" t="n">
-        <v>9.179843920030175</v>
+        <v>1.491724637004904</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
